--- a/RBM,BDM,BRANCH.xlsx
+++ b/RBM,BDM,BRANCH.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="181">
   <si>
     <t>RBM</t>
   </si>
@@ -567,6 +567,9 @@
   </si>
   <si>
     <t>THRIPUNITHURA FUTURE</t>
+  </si>
+  <si>
+    <t>CHERTHALA FUTURE</t>
   </si>
 </sst>
 </file>
@@ -1787,7 +1790,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C146"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -3380,14 +3383,25 @@
       </c>
     </row>
     <row r="145" spans="1:3">
-      <c r="A145" s="9" t="s">
+      <c r="A145" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B145" s="9" t="s">
+      <c r="B145" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C145" s="9" t="s">
+      <c r="C145" s="2" t="s">
         <v>179</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B146" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C146" s="9" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/RBM,BDM,BRANCH.xlsx
+++ b/RBM,BDM,BRANCH.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="180">
   <si>
     <t>RBM</t>
   </si>
@@ -567,9 +567,6 @@
   </si>
   <si>
     <t>THRIPUNITHURA FUTURE</t>
-  </si>
-  <si>
-    <t>CHERTHALA FUTURE</t>
   </si>
 </sst>
 </file>
@@ -1790,7 +1787,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C146"/>
+  <dimension ref="A1:C145"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -3383,25 +3380,14 @@
       </c>
     </row>
     <row r="145" spans="1:3">
-      <c r="A145" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B145" s="2" t="s">
+      <c r="A145" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B145" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C145" s="9" t="s">
         <v>179</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3">
-      <c r="A146" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B146" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C146" s="9" t="s">
-        <v>180</v>
       </c>
     </row>
   </sheetData>
